--- a/data_pipeline/selected_ultimate.xlsx
+++ b/data_pipeline/selected_ultimate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\internship\airflow\dbt_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\internship\airflow\dbt_project\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FD103E-C29E-41E3-B7A8-B0B3F4EFA02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E666B66F-4552-4C64-806D-3D5E1E70AD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{BB4E3870-83BD-4FAA-A9C5-746952296120}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="21">
   <si>
     <t>segmentation_version</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -154,10 +154,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -472,8 +473,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C469060-3846-4249-8EA2-513425B70560}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="9.3984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -625,7 +629,7 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
@@ -639,8 +643,8 @@
       <c r="F6">
         <v>2019</v>
       </c>
-      <c r="G6">
-        <v>10000</v>
+      <c r="G6" s="1">
+        <v>600</v>
       </c>
       <c r="H6" t="s">
         <v>6</v>
@@ -668,8 +672,8 @@
       <c r="F7">
         <v>2020</v>
       </c>
-      <c r="G7">
-        <v>10000</v>
+      <c r="G7" s="1">
+        <v>1100</v>
       </c>
       <c r="H7" t="s">
         <v>6</v>
@@ -697,8 +701,8 @@
       <c r="F8">
         <v>2021</v>
       </c>
-      <c r="G8">
-        <v>10000</v>
+      <c r="G8" s="1">
+        <v>1100</v>
       </c>
       <c r="H8" t="s">
         <v>6</v>
@@ -726,8 +730,8 @@
       <c r="F9">
         <v>2022</v>
       </c>
-      <c r="G9">
-        <v>10000</v>
+      <c r="G9" s="1">
+        <v>1100</v>
       </c>
       <c r="H9" t="s">
         <v>6</v>
@@ -755,13 +759,738 @@
       <c r="F10">
         <v>2023</v>
       </c>
-      <c r="G10">
-        <v>10000</v>
+      <c r="G10" s="1">
+        <v>1000</v>
       </c>
       <c r="H10" t="s">
         <v>6</v>
       </c>
       <c r="I10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11">
+        <v>2019</v>
+      </c>
+      <c r="G11" s="1">
+        <v>600</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12">
+        <v>2020</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1100</v>
+      </c>
+      <c r="H12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13">
+        <v>2021</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1100</v>
+      </c>
+      <c r="H13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14">
+        <v>2022</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1100</v>
+      </c>
+      <c r="H14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15">
+        <v>2023</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16">
+        <v>2019</v>
+      </c>
+      <c r="G16" s="1">
+        <v>600</v>
+      </c>
+      <c r="H16" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17">
+        <v>2020</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1100</v>
+      </c>
+      <c r="H17" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18">
+        <v>2021</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1100</v>
+      </c>
+      <c r="H18" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19">
+        <v>2022</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1100</v>
+      </c>
+      <c r="H19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20">
+        <v>2023</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H20" t="s">
+        <v>7</v>
+      </c>
+      <c r="I20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21">
+        <v>2019</v>
+      </c>
+      <c r="G21" s="1">
+        <v>6024871</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6</v>
+      </c>
+      <c r="I21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22">
+        <v>2020</v>
+      </c>
+      <c r="G22" s="1">
+        <v>11889980</v>
+      </c>
+      <c r="H22" t="s">
+        <v>6</v>
+      </c>
+      <c r="I22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23">
+        <v>2021</v>
+      </c>
+      <c r="G23" s="1">
+        <v>11714487</v>
+      </c>
+      <c r="H23" t="s">
+        <v>6</v>
+      </c>
+      <c r="I23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24">
+        <v>2022</v>
+      </c>
+      <c r="G24" s="1">
+        <v>12372697</v>
+      </c>
+      <c r="H24" t="s">
+        <v>6</v>
+      </c>
+      <c r="I24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25">
+        <v>2023</v>
+      </c>
+      <c r="G25" s="1">
+        <v>12153074</v>
+      </c>
+      <c r="H25" t="s">
+        <v>6</v>
+      </c>
+      <c r="I25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26">
+        <v>2019</v>
+      </c>
+      <c r="G26" s="1">
+        <v>6024871</v>
+      </c>
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27">
+        <v>2020</v>
+      </c>
+      <c r="G27" s="1">
+        <v>11889980</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28">
+        <v>2021</v>
+      </c>
+      <c r="G28" s="1">
+        <v>11714487</v>
+      </c>
+      <c r="H28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29">
+        <v>2022</v>
+      </c>
+      <c r="G29" s="1">
+        <v>12372697</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30">
+        <v>2023</v>
+      </c>
+      <c r="G30" s="1">
+        <v>12153074</v>
+      </c>
+      <c r="H30" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31">
+        <v>2019</v>
+      </c>
+      <c r="G31" s="1">
+        <v>6024871</v>
+      </c>
+      <c r="H31" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32">
+        <v>2020</v>
+      </c>
+      <c r="G32" s="1">
+        <v>11889980</v>
+      </c>
+      <c r="H32" t="s">
+        <v>7</v>
+      </c>
+      <c r="I32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33">
+        <v>2021</v>
+      </c>
+      <c r="G33" s="1">
+        <v>11714487</v>
+      </c>
+      <c r="H33" t="s">
+        <v>7</v>
+      </c>
+      <c r="I33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34">
+        <v>2022</v>
+      </c>
+      <c r="G34" s="1">
+        <v>12372697</v>
+      </c>
+      <c r="H34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35">
+        <v>2023</v>
+      </c>
+      <c r="G35" s="1">
+        <v>12153074</v>
+      </c>
+      <c r="H35" t="s">
+        <v>7</v>
+      </c>
+      <c r="I35" t="s">
         <v>13</v>
       </c>
     </row>

--- a/data_pipeline/selected_ultimate.xlsx
+++ b/data_pipeline/selected_ultimate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\internship\airflow\dbt_project\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E666B66F-4552-4C64-806D-3D5E1E70AD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3E095E-0BC0-4937-9826-EB62042323A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{BB4E3870-83BD-4FAA-A9C5-746952296120}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="21">
   <si>
     <t>segmentation_version</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -473,9 +473,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C469060-3846-4249-8EA2-513425B70560}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -641,10 +642,10 @@
         <v>11</v>
       </c>
       <c r="F6">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G6" s="1">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H6" t="s">
         <v>6</v>
@@ -670,10 +671,10 @@
         <v>11</v>
       </c>
       <c r="F7">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G7" s="1">
-        <v>1100</v>
+        <v>1201</v>
       </c>
       <c r="H7" t="s">
         <v>6</v>
@@ -699,10 +700,10 @@
         <v>11</v>
       </c>
       <c r="F8">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G8" s="1">
-        <v>1100</v>
+        <v>1202</v>
       </c>
       <c r="H8" t="s">
         <v>6</v>
@@ -728,10 +729,10 @@
         <v>11</v>
       </c>
       <c r="F9">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G9" s="1">
-        <v>1100</v>
+        <v>1203</v>
       </c>
       <c r="H9" t="s">
         <v>6</v>
@@ -757,13 +758,13 @@
         <v>11</v>
       </c>
       <c r="F10">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="G10" s="1">
-        <v>1000</v>
+        <v>1150</v>
       </c>
       <c r="H10" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s">
         <v>13</v>
@@ -786,10 +787,10 @@
         <v>11</v>
       </c>
       <c r="F11">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="G11" s="1">
-        <v>600</v>
+        <v>1151</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -815,10 +816,10 @@
         <v>11</v>
       </c>
       <c r="F12">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="G12" s="1">
-        <v>1100</v>
+        <v>1152</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
@@ -844,10 +845,10 @@
         <v>11</v>
       </c>
       <c r="F13">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G13" s="1">
-        <v>1100</v>
+        <v>1153</v>
       </c>
       <c r="H13" t="s">
         <v>14</v>
@@ -873,13 +874,13 @@
         <v>11</v>
       </c>
       <c r="F14">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="G14" s="1">
         <v>1100</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I14" t="s">
         <v>13</v>
@@ -902,13 +903,13 @@
         <v>11</v>
       </c>
       <c r="F15">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="G15" s="1">
-        <v>1000</v>
+        <v>1101</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I15" t="s">
         <v>13</v>
@@ -931,10 +932,10 @@
         <v>11</v>
       </c>
       <c r="F16">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="G16" s="1">
-        <v>600</v>
+        <v>1102</v>
       </c>
       <c r="H16" t="s">
         <v>7</v>
@@ -960,10 +961,10 @@
         <v>11</v>
       </c>
       <c r="F17">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="G17" s="1">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="H17" t="s">
         <v>7</v>
@@ -977,7 +978,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -989,13 +990,13 @@
         <v>11</v>
       </c>
       <c r="F18">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="G18" s="1">
-        <v>1100</v>
+        <v>10889980</v>
       </c>
       <c r="H18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I18" t="s">
         <v>13</v>
@@ -1006,7 +1007,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -1018,13 +1019,13 @@
         <v>11</v>
       </c>
       <c r="F19">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="G19" s="1">
-        <v>1100</v>
+        <v>10714487</v>
       </c>
       <c r="H19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I19" t="s">
         <v>13</v>
@@ -1035,7 +1036,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -1047,13 +1048,13 @@
         <v>11</v>
       </c>
       <c r="F20">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="G20" s="1">
-        <v>1000</v>
+        <v>11372697</v>
       </c>
       <c r="H20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I20" t="s">
         <v>13</v>
@@ -1076,10 +1077,10 @@
         <v>11</v>
       </c>
       <c r="F21">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="G21" s="1">
-        <v>6024871</v>
+        <v>11153074</v>
       </c>
       <c r="H21" t="s">
         <v>6</v>
@@ -1111,7 +1112,7 @@
         <v>11889980</v>
       </c>
       <c r="H22" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I22" t="s">
         <v>13</v>
@@ -1140,7 +1141,7 @@
         <v>11714487</v>
       </c>
       <c r="H23" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I23" t="s">
         <v>13</v>
@@ -1169,7 +1170,7 @@
         <v>12372697</v>
       </c>
       <c r="H24" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I24" t="s">
         <v>13</v>
@@ -1198,7 +1199,7 @@
         <v>12153074</v>
       </c>
       <c r="H25" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I25" t="s">
         <v>13</v>
@@ -1221,13 +1222,13 @@
         <v>11</v>
       </c>
       <c r="F26">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G26" s="1">
-        <v>6024871</v>
+        <v>12000000</v>
       </c>
       <c r="H26" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I26" t="s">
         <v>13</v>
@@ -1250,13 +1251,13 @@
         <v>11</v>
       </c>
       <c r="F27">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G27" s="1">
-        <v>11889980</v>
+        <v>12000001</v>
       </c>
       <c r="H27" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I27" t="s">
         <v>13</v>
@@ -1279,13 +1280,13 @@
         <v>11</v>
       </c>
       <c r="F28">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G28" s="1">
-        <v>11714487</v>
+        <v>12372692</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I28" t="s">
         <v>13</v>
@@ -1308,189 +1309,15 @@
         <v>11</v>
       </c>
       <c r="F29">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G29" s="1">
-        <v>12372697</v>
+        <v>12153073</v>
       </c>
       <c r="H29" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30">
-        <v>2023</v>
-      </c>
-      <c r="G30" s="1">
-        <v>12153074</v>
-      </c>
-      <c r="H30" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31">
-        <v>2019</v>
-      </c>
-      <c r="G31" s="1">
-        <v>6024871</v>
-      </c>
-      <c r="H31" t="s">
-        <v>7</v>
-      </c>
-      <c r="I31" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32">
-        <v>2020</v>
-      </c>
-      <c r="G32" s="1">
-        <v>11889980</v>
-      </c>
-      <c r="H32" t="s">
-        <v>7</v>
-      </c>
-      <c r="I32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33">
-        <v>2021</v>
-      </c>
-      <c r="G33" s="1">
-        <v>11714487</v>
-      </c>
-      <c r="H33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I33" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>19</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34">
-        <v>2022</v>
-      </c>
-      <c r="G34" s="1">
-        <v>12372697</v>
-      </c>
-      <c r="H34" t="s">
-        <v>7</v>
-      </c>
-      <c r="I34" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35">
-        <v>2023</v>
-      </c>
-      <c r="G35" s="1">
-        <v>12153074</v>
-      </c>
-      <c r="H35" t="s">
-        <v>7</v>
-      </c>
-      <c r="I35" t="s">
         <v>13</v>
       </c>
     </row>
